--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486441_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486441_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>I. AURRECOECHEA ALCOLADO</t>
+          <t>M. DIAZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.468299999999999</v>
+        <v>5.852</v>
       </c>
       <c r="E2" t="n">
-        <v>9.4962</v>
+        <v>8.936500000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.028</v>
+        <v>-3.0845</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.1252</v>
+        <v>-0.6347</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.3004</v>
+        <v>0.7909</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.8248</v>
+        <v>-1.4256</v>
       </c>
       <c r="J2" t="n">
-        <v>1.4473</v>
+        <v>1.9689</v>
       </c>
       <c r="K2" t="n">
-        <v>0.6823</v>
+        <v>1.8892</v>
       </c>
       <c r="L2" t="n">
-        <v>0.765</v>
+        <v>0.07969999999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.5725</v>
+        <v>-2.6036</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.9827</v>
+        <v>-1.0983</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.5898</v>
+        <v>-1.5053</v>
       </c>
       <c r="P2" t="n">
-        <v>1.305</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R2" t="n">
-        <v>1.305</v>
+        <v>0.87</v>
       </c>
       <c r="S2" t="n">
-        <v>5.8985</v>
+        <v>0.0988</v>
       </c>
       <c r="T2" t="n">
-        <v>4.659</v>
+        <v>-0.2451</v>
       </c>
       <c r="U2" t="n">
-        <v>1.2395</v>
+        <v>0.344</v>
       </c>
       <c r="V2" t="n">
-        <v>3.3899</v>
+        <v>6.6053</v>
       </c>
       <c r="W2" t="n">
-        <v>3.3899</v>
+        <v>8.3003</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-1.695</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. DIAZ</t>
+          <t>I. AURRECOECHEA ALCOLADO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.7854</v>
+        <v>5.6099</v>
       </c>
       <c r="E3" t="n">
-        <v>8.085699999999999</v>
+        <v>6.1002</v>
       </c>
       <c r="F3" t="n">
-        <v>-3.3003</v>
+        <v>-0.4903</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.6347</v>
+        <v>-1.1252</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7909</v>
+        <v>-0.3004</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.4256</v>
+        <v>-0.8248</v>
       </c>
       <c r="J3" t="n">
-        <v>1.9689</v>
+        <v>1.4473</v>
       </c>
       <c r="K3" t="n">
-        <v>1.8892</v>
+        <v>0.6823</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07969999999999999</v>
+        <v>0.765</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.6036</v>
+        <v>-2.5725</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.0983</v>
+        <v>-0.9827</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.5053</v>
+        <v>-1.5898</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.2175</v>
+        <v>1.305</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.87</v>
+        <v>1.305</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.9677</v>
+        <v>2.0402</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.0959</v>
+        <v>1.263</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1282</v>
+        <v>0.7772</v>
       </c>
       <c r="V3" t="n">
-        <v>6.6053</v>
+        <v>3.3899</v>
       </c>
       <c r="W3" t="n">
-        <v>8.3003</v>
+        <v>3.3899</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.695</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7002</v>
+        <v>1.9103</v>
       </c>
       <c r="E4" t="n">
-        <v>1.8629</v>
+        <v>2.9805</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.1627</v>
+        <v>-1.0702</v>
       </c>
       <c r="G4" t="n">
         <v>1.2548</v>
@@ -766,13 +766,13 @@
         <v>2.8276</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.9694</v>
+        <v>0.2406</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.1644</v>
+        <v>-0.0469</v>
       </c>
       <c r="U4" t="n">
-        <v>0.195</v>
+        <v>0.2875</v>
       </c>
       <c r="V4" t="n">
         <v>-1.3252</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1225</v>
+        <v>0.427</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7758</v>
+        <v>1.1111</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.6533</v>
+        <v>-0.6841</v>
       </c>
       <c r="G5" t="n">
         <v>-0.914</v>
@@ -844,13 +844,13 @@
         <v>2.1751</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.008500000000000001</v>
+        <v>0.2959</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0769</v>
+        <v>0.2584</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0684</v>
+        <v>0.0375</v>
       </c>
       <c r="V5" t="n">
         <v>-1.13</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. BELEMENE-DZABATOU</t>
+          <t>G. RENFROE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.2002</v>
+        <v>-0.912</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.4048</v>
+        <v>-2.64</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7954</v>
+        <v>1.728</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.4422</v>
+        <v>-2.0711</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5413</v>
+        <v>1.2407</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.9834</v>
+        <v>-3.3117</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.1909</v>
+        <v>-0.7935</v>
       </c>
       <c r="K8" t="n">
-        <v>1.2227</v>
+        <v>1.4599</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.4136</v>
+        <v>-2.2535</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.2512</v>
+        <v>-1.2776</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6814</v>
+        <v>-0.2193</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.5698</v>
+        <v>-1.0583</v>
       </c>
       <c r="P8" t="n">
-        <v>1.9576</v>
+        <v>0.6525</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R8" t="n">
-        <v>1.9576</v>
+        <v>2.8276</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0446</v>
+        <v>0.8763</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2139</v>
+        <v>0.1334</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2585</v>
+        <v>0.7429</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.7602</v>
+        <v>-0.3698</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.7602</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. RENFROE</t>
+          <t>J. BELEMENE-DZABATOU</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.9324</v>
+        <v>-1.3244</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.9378</v>
+        <v>-0.5598</v>
       </c>
       <c r="F9" t="n">
-        <v>2.0054</v>
+        <v>-0.7645999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.0711</v>
+        <v>-2.4422</v>
       </c>
       <c r="H9" t="n">
-        <v>1.2407</v>
+        <v>0.5413</v>
       </c>
       <c r="I9" t="n">
-        <v>-3.3117</v>
+        <v>-2.9834</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.7935</v>
+        <v>-0.1909</v>
       </c>
       <c r="K9" t="n">
-        <v>1.4599</v>
+        <v>1.2227</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.2535</v>
+        <v>-1.4136</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.2776</v>
+        <v>-2.2512</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2193</v>
+        <v>-0.6814</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.0583</v>
+        <v>-1.5698</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6525</v>
+        <v>1.9576</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.8276</v>
+        <v>1.9576</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1441</v>
+        <v>-0.0796</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.1644</v>
+        <v>-0.3689</v>
       </c>
       <c r="U9" t="n">
-        <v>1.0203</v>
+        <v>0.2893</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.3698</v>
+        <v>-0.7602</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-0.7602</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.2859</v>
+        <v>-1.9285</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.8447</v>
+        <v>-0.8879</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.4412</v>
+        <v>-1.0405</v>
       </c>
       <c r="G10" t="n">
         <v>0.0357</v>
@@ -1234,13 +1234,13 @@
         <v>2.1751</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6474</v>
+        <v>-0.2899</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2139</v>
+        <v>-0.2572</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4335</v>
+        <v>-0.0328</v>
       </c>
       <c r="V10" t="n">
         <v>-1.6743</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.025</v>
+        <v>-4.6589</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.5374</v>
+        <v>-3.2022</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.4875</v>
+        <v>-1.4567</v>
       </c>
       <c r="G11" t="n">
         <v>-5.2973</v>
@@ -1312,13 +1312,13 @@
         <v>1.0875</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.62</v>
+        <v>-0.2539</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6850000000000001</v>
+        <v>-0.3497</v>
       </c>
       <c r="U11" t="n">
-        <v>0.065</v>
+        <v>0.0958</v>
       </c>
       <c r="V11" t="n">
         <v>-0.1952</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.530899999999997</v>
+        <v>4.873399999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>11.4274</v>
+        <v>11.7699</v>
       </c>
       <c r="F12" t="n">
-        <v>-6.896500000000001</v>
+        <v>-6.8964</v>
       </c>
       <c r="G12" t="n">
         <v>-11.2275</v>
@@ -1390,10 +1390,10 @@
         <v>15.2255</v>
       </c>
       <c r="S12" t="n">
-        <v>2.5175</v>
+        <v>2.859900000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.02390000000000048</v>
+        <v>0.3184999999999998</v>
       </c>
       <c r="U12" t="n">
         <v>2.5414</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.433</v>
+        <v>2.7104</v>
       </c>
       <c r="E13" t="n">
         <v>4.6078</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.1748</v>
+        <v>-1.8974</v>
       </c>
       <c r="G13" t="n">
         <v>2.2147</v>
@@ -1468,13 +1468,13 @@
         <v>0.435</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.649</v>
+        <v>-0.3716</v>
       </c>
       <c r="T13" t="n">
         <v>-0.008399999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6405999999999999</v>
+        <v>-0.3632</v>
       </c>
       <c r="V13" t="n">
         <v>2.8249</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.9775</v>
+        <v>1.3609</v>
       </c>
       <c r="E14" t="n">
-        <v>3.2578</v>
+        <v>2.3637</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.2803</v>
+        <v>-1.0029</v>
       </c>
       <c r="G14" t="n">
         <v>1.0988</v>
@@ -1546,13 +1546,13 @@
         <v>0.87</v>
       </c>
       <c r="S14" t="n">
-        <v>0.7281</v>
+        <v>0.1115</v>
       </c>
       <c r="T14" t="n">
-        <v>0.7282</v>
+        <v>-0.1658</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0001</v>
+        <v>0.2773</v>
       </c>
       <c r="V14" t="n">
         <v>0.5857</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.2675</v>
+        <v>1.3214</v>
       </c>
       <c r="E15" t="n">
-        <v>2.6909</v>
+        <v>2.4674</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.4234</v>
+        <v>-1.146</v>
       </c>
       <c r="G15" t="n">
         <v>3.103</v>
@@ -1624,13 +1624,13 @@
         <v>0.6525</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2705</v>
+        <v>-0.2166</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.008399999999999999</v>
+        <v>-0.2319</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2621</v>
+        <v>0.0153</v>
       </c>
       <c r="V15" t="n">
         <v>-1.13</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0137</v>
+        <v>0.5145999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>3.4981</v>
+        <v>3.7216</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.4844</v>
+        <v>-3.207</v>
       </c>
       <c r="G16" t="n">
         <v>1.4314</v>
@@ -1702,13 +1702,13 @@
         <v>1.0875</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.8305</v>
+        <v>-0.3296</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8304</v>
+        <v>-0.6068</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0001</v>
+        <v>0.2773</v>
       </c>
       <c r="V16" t="n">
         <v>-0.3698</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2749</v>
+        <v>-0.0091</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.4151</v>
+        <v>-0.3033</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1401</v>
+        <v>0.2942</v>
       </c>
       <c r="G17" t="n">
         <v>1.5456</v>
@@ -1780,13 +1780,13 @@
         <v>0.2175</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5377999999999999</v>
+        <v>-0.2719</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3425</v>
+        <v>-0.2307</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1953</v>
+        <v>-0.0412</v>
       </c>
       <c r="V17" t="n">
         <v>-0.1952</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>U. MENDICOTE RUBIO</t>
+          <t>S. HOLLANDERS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4867</v>
+        <v>-0.1585</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9464</v>
+        <v>2.2206</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.4331</v>
+        <v>-2.379</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.9492</v>
+        <v>2.7548</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.4568</v>
+        <v>1.1707</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5076000000000001</v>
+        <v>1.5842</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4375</v>
+        <v>3.081</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.9395</v>
+        <v>1.6059</v>
       </c>
       <c r="L18" t="n">
-        <v>1.377</v>
+        <v>1.475</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.3867</v>
+        <v>-0.3261</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5173</v>
+        <v>-0.4353</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.8694</v>
+        <v>0.1091</v>
       </c>
       <c r="P18" t="n">
-        <v>0.2175</v>
+        <v>0.435</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.2175</v>
+        <v>-0.435</v>
       </c>
       <c r="R18" t="n">
-        <v>0.435</v>
+        <v>0.87</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4402</v>
+        <v>-0.8932</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5312</v>
+        <v>-0.4254</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.091</v>
+        <v>-0.4678</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.1952</v>
+        <v>-2.4552</v>
       </c>
       <c r="W18" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.3904</v>
+        <v>-2.4552</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.7499</v>
+        <v>-0.8038</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.8923</v>
+        <v>-0.6688</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1425</v>
+        <v>-0.1349</v>
       </c>
       <c r="G19" t="n">
         <v>-0.4212</v>
@@ -1936,13 +1936,13 @@
         <v>0.435</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0035</v>
+        <v>-0.0574</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8904</v>
+        <v>-0.6669</v>
       </c>
       <c r="U19" t="n">
-        <v>0.887</v>
+        <v>0.6096</v>
       </c>
       <c r="V19" t="n">
         <v>-0.7602</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>B. COULIBALY</t>
+          <t>U. MENDICOTE RUBIO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.0051</v>
+        <v>-1.1495</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.6405</v>
+        <v>0.4994</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3646</v>
+        <v>-1.6489</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7346</v>
+        <v>-0.9492</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1003</v>
+        <v>-1.4568</v>
       </c>
       <c r="I20" t="n">
-        <v>0.6343</v>
+        <v>0.5076000000000001</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0565</v>
+        <v>0.4375</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0182</v>
+        <v>-0.9395</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0382</v>
+        <v>1.377</v>
       </c>
       <c r="M20" t="n">
-        <v>0.6781</v>
+        <v>-1.3867</v>
       </c>
       <c r="N20" t="n">
-        <v>0.082</v>
+        <v>-0.5173</v>
       </c>
       <c r="O20" t="n">
-        <v>0.596</v>
+        <v>-0.8694</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.0875</v>
+        <v>0.2175</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.305</v>
+        <v>-0.2175</v>
       </c>
       <c r="R20" t="n">
-        <v>0.2175</v>
+        <v>0.435</v>
       </c>
       <c r="S20" t="n">
-        <v>0.6731</v>
+        <v>-0.2226</v>
       </c>
       <c r="T20" t="n">
-        <v>0.6081</v>
+        <v>0.08409999999999999</v>
       </c>
       <c r="U20" t="n">
-        <v>0.065</v>
+        <v>-0.3067</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.3252</v>
+        <v>-0.1952</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.3252</v>
+        <v>-0.3904</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S. HOLLANDERS</t>
+          <t>B. COULIBALY</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.1064</v>
+        <v>-1.4213</v>
       </c>
       <c r="E21" t="n">
-        <v>1.55</v>
+        <v>-1.0875</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.6564</v>
+        <v>-0.3338</v>
       </c>
       <c r="G21" t="n">
-        <v>2.7548</v>
+        <v>0.7346</v>
       </c>
       <c r="H21" t="n">
-        <v>1.1707</v>
+        <v>0.1003</v>
       </c>
       <c r="I21" t="n">
-        <v>1.5842</v>
+        <v>0.6343</v>
       </c>
       <c r="J21" t="n">
-        <v>3.081</v>
+        <v>0.0565</v>
       </c>
       <c r="K21" t="n">
-        <v>1.6059</v>
+        <v>0.0182</v>
       </c>
       <c r="L21" t="n">
-        <v>1.475</v>
+        <v>0.0382</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.3261</v>
+        <v>0.6781</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.4353</v>
+        <v>0.082</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1091</v>
+        <v>0.596</v>
       </c>
       <c r="P21" t="n">
-        <v>0.435</v>
+        <v>-1.0875</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.435</v>
+        <v>-1.305</v>
       </c>
       <c r="R21" t="n">
-        <v>0.87</v>
+        <v>0.2175</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.8411</v>
+        <v>0.2569</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.0959</v>
+        <v>0.161</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.7452</v>
+        <v>0.0958</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.4552</v>
+        <v>-1.3252</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.4552</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>I. TAMBA VILLEN</t>
+          <t>S. CECCARDI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.7227</v>
+        <v>-1.6243</v>
       </c>
       <c r="E22" t="n">
-        <v>0.2176</v>
+        <v>-2.2932</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.9403</v>
+        <v>0.6689000000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>1.2108</v>
+        <v>1.7519</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2403</v>
+        <v>0.1733</v>
       </c>
       <c r="I22" t="n">
-        <v>0.9706</v>
+        <v>1.5786</v>
       </c>
       <c r="J22" t="n">
-        <v>0.5177</v>
+        <v>1.1941</v>
       </c>
       <c r="K22" t="n">
-        <v>0.4412</v>
+        <v>-0.1063</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0765</v>
+        <v>1.3005</v>
       </c>
       <c r="M22" t="n">
-        <v>0.6932</v>
+        <v>0.5577</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.2009</v>
+        <v>0.2796</v>
       </c>
       <c r="O22" t="n">
-        <v>0.8941</v>
+        <v>0.2781</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.87</v>
+        <v>-3.0451</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.0875</v>
+        <v>-3.4801</v>
       </c>
       <c r="R22" t="n">
-        <v>0.2175</v>
+        <v>0.435</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5431</v>
+        <v>-0.3311</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3425</v>
+        <v>-0.0072</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2006</v>
+        <v>-0.3239</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.5204</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.6504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S. CECCARDI</t>
+          <t>I. TAMBA VILLEN</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.7746</v>
+        <v>-1.7766</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.6284</v>
+        <v>0.4411</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8538</v>
+        <v>-2.2177</v>
       </c>
       <c r="G23" t="n">
-        <v>1.7519</v>
+        <v>1.2108</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1733</v>
+        <v>0.2403</v>
       </c>
       <c r="I23" t="n">
-        <v>1.5786</v>
+        <v>0.9706</v>
       </c>
       <c r="J23" t="n">
-        <v>1.1941</v>
+        <v>0.5177</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.1063</v>
+        <v>0.4412</v>
       </c>
       <c r="L23" t="n">
-        <v>1.3005</v>
+        <v>0.0765</v>
       </c>
       <c r="M23" t="n">
-        <v>0.5577</v>
+        <v>0.6932</v>
       </c>
       <c r="N23" t="n">
-        <v>0.2796</v>
+        <v>-0.2009</v>
       </c>
       <c r="O23" t="n">
-        <v>0.2781</v>
+        <v>0.8941</v>
       </c>
       <c r="P23" t="n">
-        <v>-3.0451</v>
+        <v>-0.87</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.4801</v>
+        <v>-1.0875</v>
       </c>
       <c r="R23" t="n">
-        <v>0.435</v>
+        <v>0.2175</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4814</v>
+        <v>-0.5969</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3425</v>
+        <v>-0.119</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1389</v>
+        <v>-0.478</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-1.5204</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-2.6504</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.1022</v>
+        <v>-3.4952</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.2958</v>
+        <v>-5.0723</v>
       </c>
       <c r="F24" t="n">
-        <v>2.1936</v>
+        <v>1.5771</v>
       </c>
       <c r="G24" t="n">
         <v>-3.2476</v>
@@ -2326,13 +2326,13 @@
         <v>0.6525</v>
       </c>
       <c r="S24" t="n">
-        <v>0.7979000000000001</v>
+        <v>0.405</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.548</v>
+        <v>-0.3245</v>
       </c>
       <c r="U24" t="n">
-        <v>1.3459</v>
+        <v>0.7294</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.5308</v>
+        <v>-4.531000000000001</v>
       </c>
       <c r="E25" t="n">
         <v>6.8965</v>
       </c>
       <c r="F25" t="n">
-        <v>-11.4273</v>
+        <v>-11.4274</v>
       </c>
       <c r="G25" t="n">
         <v>11.2276</v>
@@ -2389,13 +2389,13 @@
         <v>-6.0498</v>
       </c>
       <c r="N25" t="n">
-        <v>-7.240999999999999</v>
+        <v>-7.241</v>
       </c>
       <c r="O25" t="n">
         <v>1.1911</v>
       </c>
       <c r="P25" t="n">
-        <v>-8.700200000000001</v>
+        <v>-8.700199999999999</v>
       </c>
       <c r="Q25" t="n">
         <v>-15.2252</v>
@@ -2404,13 +2404,13 @@
         <v>6.524999999999999</v>
       </c>
       <c r="S25" t="n">
-        <v>-2.5176</v>
+        <v>-2.5175</v>
       </c>
       <c r="T25" t="n">
-        <v>-2.5415</v>
+        <v>-2.541500000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>0.02400000000000024</v>
+        <v>0.02390000000000003</v>
       </c>
       <c r="V25" t="n">
         <v>-4.5406</v>
